--- a/deliverables/tabulation-plan/tabulation-decision-tracker-2026-07-06.xlsx
+++ b/deliverables/tabulation-plan/tabulation-decision-tracker-2026-07-06.xlsx
@@ -1405,7 +1405,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Adopt the standard method (brief §3B); approve as a set.</t>
+          <t>Compute on F4 (household), Capacity-to-Pay: health OOP ÷ (total household spending − food Q157), at 25% &amp; 40%. F4 Section N already collects this — see CTP alignment note. (Replaces 'OOP ÷ income'.)</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr"/>
